--- a/data1_new.xlsx
+++ b/data1_new.xlsx
@@ -1024,7 +1024,7 @@
         <v>118</v>
       </c>
       <c r="F27" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28">
